--- a/artfynd/A 50822-2025 artfynd.xlsx
+++ b/artfynd/A 50822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224160</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50822-2025 artfynd.xlsx
+++ b/artfynd/A 50822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224160</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50822-2025 artfynd.xlsx
+++ b/artfynd/A 50822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224160</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50822-2025 artfynd.xlsx
+++ b/artfynd/A 50822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224160</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50822-2025 artfynd.xlsx
+++ b/artfynd/A 50822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129224160</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50822-2025 artfynd.xlsx
+++ b/artfynd/A 50822-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>129224160</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
